--- a/docs/Athens_Audit_Checklists_for_Review.xlsx
+++ b/docs/Athens_Audit_Checklists_for_Review.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Operations Yard</t>
+          <t>Hauling Yard</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
